--- a/feedback_forms/005_watched_content_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/005_watched_content_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>Did you watch the content?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_2</t>
+          <t>watched_content_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>watched_content</t>
+          <t>What type of content was it?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>watched_content_feedback_rating</t>
+          <t>watched_content_count</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>watched_content_feedback_rating</t>
+          <t>How many times did you watch it?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,104 +589,104 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>watched_content_feedback_rating_comment</t>
+          <t>watched_content_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>watched_content_feedback_rating_comment</t>
+          <t>What was the rating?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_5</t>
+          <t>watched_content_comment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>What was your comment on the content?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_6</t>
+          <t>watched_content_watched_again</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>Would you watch it again?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_7</t>
+          <t>watched_content_watched_at</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>When was the last time you watched it?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_8</t>
+          <t>watched_content_watched_at_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>What time did you watch it?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_9</t>
+          <t>watched_content_access_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>How did you access the content?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_10</t>
+          <t>watched_content_relevance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>watched_content_feedback</t>
+          <t>Was the content relevant to you?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>watched_content_followability</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Was the content easy to follow?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>watched_content_other_comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Any other comments?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -803,80 +849,165 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_2_choices</t>
+          <t>watched_content_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_2_choices</t>
+          <t>watched_content_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_10_choices</t>
+          <t>watched_content_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>watched_content_feedback_form_10_choices</t>
+          <t>watched_content_watched_again_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>watched_content_watched_again_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>watched_content_relevance_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>watched_content_relevance_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>watched_content_followability_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>watched_content_followability_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
